--- a/outputs/week3_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week3_excel/001282_三联锻造_三表抽取.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2019年12月4日，公司召开2019年第二次临时股东大会，审议通过了《关于公司增资扩股的议案》，议案决定拟将公司的注册资本由8,150万元增加至8,498万元。新增注册资本由新股东三联合伙以每股4.50元的价格认购，其中348万元计入注册资本，剩余1,218万元计入资本公积。</t>
+          <t>2019年12月4日，公司召开2019年第二次临时股东大会，审议通过了《关于公司增资扩股的议案》，议案决定拟将公司的注册资本由 8,150 万元增加至8,498万元。新增注册资本由新股东三联合伙以每股 4.50元的价格认购，其中 348 万元计入注册资本，剩余 1,218万元计入资本公积。</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,7 +669,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>货币出资置换完成后（2007年11月）</t>
+          <t>货币出资置换完成后三联有限的出资结构（2007年11月）</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -690,7 +690,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%</t>
+          <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>货币出资置换完成后（2007年11月）</t>
+          <t>货币出资置换完成后三联有限的出资结构（2007年11月）</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -726,7 +726,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国敏货币出资100万元，占注册资本20%</t>
+          <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国敏货币出资100万元</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>货币出资置换完成后（2007年11月）</t>
+          <t>货币出资置换完成后三联有限的出资结构（2007年11月）</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -762,7 +762,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>本次货币出资置换完成后，三联有限的出资结构如下：张松满货币出资105万元，占注册资本21%</t>
+          <t>本次货币出资置换完成后，三联有限的出资结构如下：张松满货币出资105万元</t>
         </is>
       </c>
     </row>
@@ -794,63 +794,65 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2018年10月27日，公司召开创立大会暨第一次临时股东大会并作出决议，全体股东（发起人）一致同意通过关于整体变更为股份公司的相关议案。</t>
+          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>股份公司设立时股权结构（2018年11月）</t>
+          <t>2019年12月增资后股权结构</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8150</v>
+        <v>8498</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>张一衡</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>三联合伙</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>348</v>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2018年10月27日，公司召开创立大会暨第一次临时股东大会并作出决议，全体股东（发起人）一致同意通过关于整体变更为股份公司的相关议案。</t>
+          <t>本次增资完成后，公司股本结构如下：三联合伙持股348万股</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>股份公司设立时股权结构（2018年11月）</t>
+          <t>本次发行前股权结构（截至招股说明书签署日）</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8150</v>
+        <v>8498</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -858,31 +860,31 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2018年10月27日，公司召开创立大会暨第一次临时股东大会并作出决议，全体股东（发起人）一致同意通过关于整体变更为股份公司的相关议案。</t>
+          <t>截至本招股说明书签署日，孙国奉直接持有公司 26.91%的股份</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>股份公司设立时股权结构（2018年11月）</t>
+          <t>本次发行前股权结构（截至招股说明书签署日）</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8150</v>
+        <v>8498</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>孙仁豪</t>
+          <t>张一衡</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -890,31 +892,31 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2018年10月27日，公司召开创立大会暨第一次临时股东大会并作出决议，全体股东（发起人）一致同意通过关于整体变更为股份公司的相关议案。</t>
+          <t>截至本招股说明书签署日，张一衡直接持有公司 26.77%的股份</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>t4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>股份公司设立时股权结构（2018年11月）</t>
+          <t>本次发行前股权结构（截至招股说明书签署日）</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8150</v>
+        <v>8498</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -922,22 +924,22 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2018年10月27日，公司召开创立大会暨第一次临时股东大会并作出决议，全体股东（发起人）一致同意通过关于整体变更为股份公司的相关议案。</t>
+          <t>截至本招股说明书签署日，孙国敏直接持有公司 26.77%的股份</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2019年12月增资后股权结构</t>
+          <t>本次发行前股权结构（截至招股说明书签署日）</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -946,7 +948,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>孙国奉</t>
+          <t>孙仁豪</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -954,22 +956,22 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>本次增资完成后，公司股本结构如下：</t>
+          <t>截至本招股说明书签署日，孙仁豪直接持有公司 1.92%的股份</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2019年12月增资后股权结构</t>
+          <t>本次发行前股权结构（截至招股说明书签署日）</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -978,7 +980,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>张一衡</t>
+          <t>三联合伙</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -986,22 +988,22 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>本次增资完成后，公司股本结构如下：</t>
+          <t>孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>t4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2019年12月增资后股权结构</t>
+          <t>本次发行前股权结构（截至招股说明书签署日）</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1010,7 +1012,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1018,295 +1020,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>本次增资完成后，公司股本结构如下：</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>38</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>t3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2019年12月增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>8498</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>孙仁豪</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>本次增资完成后，公司股本结构如下：</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>38</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>t3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2019年12月增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>8498</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>本次增资完成后，公司股本结构如下：</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>38</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>t3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2019年12月增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>8498</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>三联合伙</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>本次增资完成后，公司股本结构如下：</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>53</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>t4</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>本次发行前股权结构（截至招股说明书签署日）</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>8498</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>53</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>t4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>本次发行前股权结构（截至招股说明书签署日）</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>8498</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>张一衡</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>张一衡直接持有公司26.77%的股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>53</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>t4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>本次发行前股权结构（截至招股说明书签署日）</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>8498</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>孙国敏直接持有公司26.77%的股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>53</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>t4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>本次发行前股权结构（截至招股说明书签署日）</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8498</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>孙仁豪</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>孙仁豪直接持有公司1.92%的股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>53</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>t4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>本次发行前股权结构（截至招股说明书签署日）</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>8498</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>高新同华直接持有公司13.53%的股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>53</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>t4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>本次发行前股权结构（截至招股说明书签署日）</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>8498</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>三联合伙</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权</t>
+          <t>截至本招股说明书签署日，高新同华直接持有公司 13.53%的股份</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1240,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -1559,9 +1273,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>348</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
